--- a/hss-w26.xlsx
+++ b/hss-w26.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kenlo\Desktop\2526_Winter_SFQ_Data\File Upload to AQA website\Regen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gohkust.sharepoint.com/teams/SEA/Shared Documents/SFQ/2526 Winter/Ken_Draft/File Upload to AQA website/Regen_New/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{790A508F-04B4-4E4C-B886-3183BCC7CC0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{790A508F-04B4-4E4C-B886-3183BCC7CC0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{157D0BA2-ADDE-471A-8D28-4AFB0E36E70A}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{D0CD8A38-F1F2-4D79-8B06-93118E2B8226}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{D0CD8A38-F1F2-4D79-8B06-93118E2B8226}"/>
   </bookViews>
   <sheets>
     <sheet name="School_Term_Summary_Report-SHSS" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="45">
   <si>
     <t>Academic Year</t>
   </si>
@@ -73,34 +73,19 @@
     <t>Low Response Rate Indicator</t>
   </si>
   <si>
-    <t>Response Rate (Adjusted)</t>
-  </si>
-  <si>
     <t>No. of Sections Evaluated</t>
   </si>
   <si>
     <t>Course Overall - Mean</t>
   </si>
   <si>
-    <t>Course Overall - Mean (Adjusted)</t>
-  </si>
-  <si>
     <t>Course Overall - SD</t>
   </si>
   <si>
-    <t>Course Overall - SD (Adjusted)</t>
-  </si>
-  <si>
     <t>Instructor Overall - Mean</t>
   </si>
   <si>
-    <t>Instructor Overall - Mean (Adjusted)</t>
-  </si>
-  <si>
     <t>Instructor Overall - SD</t>
-  </si>
-  <si>
-    <t>Instructor Overall - SD (Adjusted)</t>
   </si>
   <si>
     <t>25-26</t>
@@ -1032,10 +1017,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BCFB3B9-2BC6-4BFA-BDB6-7501A84084F3}">
-  <dimension ref="A1:AA18"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1102,268 +1087,253 @@
       <c r="V1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="B2" t="s">
         <v>23</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" t="s">
-        <v>28</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P2" s="1">
         <v>0.6</v>
       </c>
       <c r="Q2" t="s">
-        <v>30</v>
+        <v>25</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
       </c>
       <c r="S2">
-        <v>1</v>
+        <v>4.8899999999999997</v>
       </c>
       <c r="T2">
-        <v>4.8899999999999997</v>
+        <v>0.33</v>
+      </c>
+      <c r="U2">
+        <v>5</v>
       </c>
       <c r="V2">
-        <v>0.33</v>
-      </c>
-      <c r="X2">
-        <v>5</v>
-      </c>
-      <c r="Z2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" t="s">
-        <v>32</v>
-      </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P3" s="1">
         <v>0.6</v>
       </c>
       <c r="Q3" t="s">
-        <v>33</v>
+        <v>28</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
       </c>
       <c r="S3">
-        <v>1</v>
+        <v>4.8899999999999997</v>
       </c>
       <c r="T3">
-        <v>4.8899999999999997</v>
+        <v>0.33</v>
+      </c>
+      <c r="U3">
+        <v>5</v>
       </c>
       <c r="V3">
-        <v>0.33</v>
-      </c>
-      <c r="X3">
-        <v>5</v>
-      </c>
-      <c r="Z3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
         <v>27</v>
       </c>
-      <c r="B4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" t="s">
-        <v>32</v>
-      </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G4">
         <v>5880</v>
       </c>
       <c r="H4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" t="s">
         <v>30</v>
       </c>
-      <c r="I4" t="s">
-        <v>35</v>
-      </c>
       <c r="J4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P4" s="1">
         <v>0.6</v>
       </c>
       <c r="Q4" t="s">
-        <v>33</v>
+        <v>28</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
       </c>
       <c r="S4">
-        <v>1</v>
+        <v>4.8899999999999997</v>
       </c>
       <c r="T4">
-        <v>4.8899999999999997</v>
+        <v>0.33</v>
+      </c>
+      <c r="U4">
+        <v>5</v>
       </c>
       <c r="V4">
-        <v>0.33</v>
-      </c>
-      <c r="X4">
-        <v>5</v>
-      </c>
-      <c r="Z4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G5">
         <v>5880</v>
       </c>
       <c r="H5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="K5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O5">
         <v>15</v>
@@ -1372,66 +1342,66 @@
         <v>0.6</v>
       </c>
       <c r="Q5" t="s">
+        <v>28</v>
+      </c>
+      <c r="R5" t="s">
+        <v>25</v>
+      </c>
+      <c r="S5">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="T5">
+        <v>0.33</v>
+      </c>
+      <c r="U5">
+        <v>5</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
         <v>33</v>
       </c>
-      <c r="S5" t="s">
-        <v>30</v>
-      </c>
-      <c r="T5">
-        <v>4.8899999999999997</v>
-      </c>
-      <c r="V5">
-        <v>0.33</v>
-      </c>
-      <c r="X5">
-        <v>5</v>
-      </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
         <v>27</v>
       </c>
-      <c r="B6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" t="s">
-        <v>32</v>
-      </c>
       <c r="F6" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G6">
         <v>5880</v>
       </c>
       <c r="H6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" t="s">
+        <v>34</v>
+      </c>
+      <c r="M6" t="s">
+        <v>35</v>
+      </c>
+      <c r="N6" t="s">
         <v>36</v>
-      </c>
-      <c r="I6" t="s">
-        <v>35</v>
-      </c>
-      <c r="J6" t="s">
-        <v>37</v>
-      </c>
-      <c r="K6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L6" t="s">
-        <v>39</v>
-      </c>
-      <c r="M6" t="s">
-        <v>40</v>
-      </c>
-      <c r="N6" t="s">
-        <v>41</v>
       </c>
       <c r="O6">
         <v>15</v>
@@ -1440,62 +1410,62 @@
         <v>0.6</v>
       </c>
       <c r="Q6" t="s">
-        <v>33</v>
-      </c>
-      <c r="S6" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="R6" t="s">
+        <v>25</v>
+      </c>
+      <c r="S6">
+        <v>4.8899999999999997</v>
       </c>
       <c r="T6">
-        <v>4.8899999999999997</v>
+        <v>0.33</v>
+      </c>
+      <c r="U6">
+        <v>5</v>
       </c>
       <c r="V6">
-        <v>0.33</v>
-      </c>
-      <c r="X6">
-        <v>5</v>
-      </c>
-      <c r="Z6">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
@@ -1509,6 +1479,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064FBF1EC94D9E9419E928C7F04731A98" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d5d1fc6aea0bdb544d42f3777360a695">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="307c76f0-d205-4835-9aae-d70c69349486" xmlns:ns3="c1544048-3019-4d62-a7f3-2ad0cae9f9e9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="91955e799b8657f65baef53610b4215d" ns2:_="" ns3:_="">
     <xsd:import namespace="307c76f0-d205-4835-9aae-d70c69349486"/>
@@ -1757,15 +1736,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1778,13 +1748,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4A6314F-D7CB-46DA-AA86-827B442A24E0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75766FAB-DD09-4245-8298-DF5F886F477D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75766FAB-DD09-4245-8298-DF5F886F477D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4A6314F-D7CB-46DA-AA86-827B442A24E0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="307c76f0-d205-4835-9aae-d70c69349486"/>
+    <ds:schemaRef ds:uri="c1544048-3019-4d62-a7f3-2ad0cae9f9e9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39E944F1-96FE-4737-BC0E-93E7D6002D9E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39E944F1-96FE-4737-BC0E-93E7D6002D9E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="307c76f0-d205-4835-9aae-d70c69349486"/>
+    <ds:schemaRef ds:uri="c1544048-3019-4d62-a7f3-2ad0cae9f9e9"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/hss-w26.xlsx
+++ b/hss-w26.xlsx
@@ -5,22 +5,22 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gohkust.sharepoint.com/teams/SEA/Shared Documents/SFQ/2526 Winter/Ken_Draft/File Upload to AQA website/Regen_New/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gohkust.sharepoint.com/teams/SEA/Shared Documents/SFQ/2526 Winter/Ken_Draft/File Upload to AQA website/Regen_Mar13/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{790A508F-04B4-4E4C-B886-3183BCC7CC0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{157D0BA2-ADDE-471A-8D28-4AFB0E36E70A}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{3ADAA5A3-0627-42F9-BD13-8DCFE57EED8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B09859E3-2DD3-4C30-9481-EEEEEC0BAA1A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{D0CD8A38-F1F2-4D79-8B06-93118E2B8226}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{6A55011A-406F-4B67-90EB-815396E0FF4A}"/>
   </bookViews>
   <sheets>
-    <sheet name="School_Term_Summary_Report-SHSS" sheetId="1" r:id="rId1"/>
+    <sheet name="hss-w26" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="46">
   <si>
     <t>Academic Year</t>
   </si>
@@ -71,6 +71,9 @@
   </si>
   <si>
     <t>Low Response Rate Indicator</t>
+  </si>
+  <si>
+    <t>Response Rate (Adjusted)</t>
   </si>
   <si>
     <t>No. of Sections Evaluated</t>
@@ -1016,11 +1019,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BCFB3B9-2BC6-4BFA-BDB6-7501A84084F3}">
-  <dimension ref="A1:V18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF31CCBA-634B-4108-BFB6-D37F4541E527}">
+  <dimension ref="A1:W18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1087,253 +1090,256 @@
       <c r="V1" t="s">
         <v>21</v>
       </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P2" s="1">
         <v>0.6</v>
       </c>
       <c r="Q2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+      <c r="T2">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="U2">
+        <v>0.33</v>
+      </c>
+      <c r="V2">
+        <v>5</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
         <v>25</v>
       </c>
-      <c r="R2">
-        <v>1</v>
-      </c>
-      <c r="S2">
-        <v>4.8899999999999997</v>
-      </c>
-      <c r="T2">
-        <v>0.33</v>
-      </c>
-      <c r="U2">
-        <v>5</v>
-      </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P3" s="1">
         <v>0.6</v>
       </c>
       <c r="Q3" t="s">
+        <v>29</v>
+      </c>
+      <c r="S3">
+        <v>1</v>
+      </c>
+      <c r="T3">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="U3">
+        <v>0.33</v>
+      </c>
+      <c r="V3">
+        <v>5</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
         <v>28</v>
       </c>
-      <c r="R3">
-        <v>1</v>
-      </c>
-      <c r="S3">
-        <v>4.8899999999999997</v>
-      </c>
-      <c r="T3">
-        <v>0.33</v>
-      </c>
-      <c r="U3">
-        <v>5</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" t="s">
-        <v>27</v>
-      </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G4">
         <v>5880</v>
       </c>
       <c r="H4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P4" s="1">
         <v>0.6</v>
       </c>
       <c r="Q4" t="s">
-        <v>28</v>
-      </c>
-      <c r="R4">
+        <v>29</v>
+      </c>
+      <c r="S4">
         <v>1</v>
       </c>
-      <c r="S4">
+      <c r="T4">
         <v>4.8899999999999997</v>
       </c>
-      <c r="T4">
+      <c r="U4">
         <v>0.33</v>
       </c>
-      <c r="U4">
+      <c r="V4">
         <v>5</v>
       </c>
-      <c r="V4">
+      <c r="W4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G5">
         <v>5880</v>
       </c>
       <c r="H5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" t="s">
         <v>31</v>
       </c>
-      <c r="I5" t="s">
-        <v>30</v>
-      </c>
       <c r="J5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O5">
         <v>15</v>
@@ -1342,66 +1348,66 @@
         <v>0.6</v>
       </c>
       <c r="Q5" t="s">
+        <v>29</v>
+      </c>
+      <c r="S5" t="s">
+        <v>26</v>
+      </c>
+      <c r="T5">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="U5">
+        <v>0.33</v>
+      </c>
+      <c r="V5">
+        <v>5</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
         <v>28</v>
       </c>
-      <c r="R5" t="s">
-        <v>25</v>
-      </c>
-      <c r="S5">
-        <v>4.8899999999999997</v>
-      </c>
-      <c r="T5">
-        <v>0.33</v>
-      </c>
-      <c r="U5">
-        <v>5</v>
-      </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" t="s">
-        <v>27</v>
-      </c>
       <c r="F6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G6">
         <v>5880</v>
       </c>
       <c r="H6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" t="s">
         <v>31</v>
       </c>
-      <c r="I6" t="s">
-        <v>30</v>
-      </c>
       <c r="J6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O6">
         <v>15</v>
@@ -1410,67 +1416,67 @@
         <v>0.6</v>
       </c>
       <c r="Q6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R6" t="s">
-        <v>25</v>
-      </c>
-      <c r="S6">
+        <v>29</v>
+      </c>
+      <c r="S6" t="s">
+        <v>26</v>
+      </c>
+      <c r="T6">
         <v>4.8899999999999997</v>
       </c>
-      <c r="T6">
+      <c r="U6">
         <v>0.33</v>
       </c>
-      <c r="U6">
+      <c r="V6">
         <v>5</v>
       </c>
-      <c r="V6">
+      <c r="W6">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>46082</v>
+        <v>46094</v>
       </c>
     </row>
   </sheetData>
@@ -1748,7 +1754,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75766FAB-DD09-4245-8298-DF5F886F477D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B1C7573-D4C2-4CC9-AEAF-DBFC93DE5FD3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -1756,7 +1762,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4A6314F-D7CB-46DA-AA86-827B442A24E0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{893E3792-6E1A-4ACB-8552-B86A077B5A4D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -1775,7 +1781,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39E944F1-96FE-4737-BC0E-93E7D6002D9E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{013CA3C2-86F0-4056-AE8C-432415CDD608}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>

--- a/hss-w26.xlsx
+++ b/hss-w26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gohkust.sharepoint.com/teams/SEA/Shared Documents/SFQ/2526 Winter/Ken_Draft/File Upload to AQA website/Regen_Mar13/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{3ADAA5A3-0627-42F9-BD13-8DCFE57EED8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B09859E3-2DD3-4C30-9481-EEEEEC0BAA1A}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{3ADAA5A3-0627-42F9-BD13-8DCFE57EED8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{298C1290-68E1-44DA-A445-E6FBEDAB319A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{6A55011A-406F-4B67-90EB-815396E0FF4A}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="45">
   <si>
     <t>Academic Year</t>
   </si>
@@ -71,9 +71,6 @@
   </si>
   <si>
     <t>Low Response Rate Indicator</t>
-  </si>
-  <si>
-    <t>Response Rate (Adjusted)</t>
   </si>
   <si>
     <t>No. of Sections Evaluated</t>
@@ -1020,10 +1017,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF31CCBA-634B-4108-BFB6-D37F4541E527}">
-  <dimension ref="A1:W18"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1090,256 +1087,253 @@
       <c r="V1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>23</v>
-      </c>
-      <c r="B2" t="s">
-        <v>24</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P2" s="1">
         <v>0.6</v>
       </c>
       <c r="Q2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="T2">
+        <v>0.33</v>
+      </c>
+      <c r="U2">
+        <v>5</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
         <v>26</v>
       </c>
-      <c r="S2">
-        <v>1</v>
-      </c>
-      <c r="T2">
-        <v>4.8899999999999997</v>
-      </c>
-      <c r="U2">
-        <v>0.33</v>
-      </c>
-      <c r="V2">
-        <v>5</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
         <v>24</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>27</v>
       </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" t="s">
-        <v>28</v>
-      </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P3" s="1">
         <v>0.6</v>
       </c>
       <c r="Q3" t="s">
+        <v>28</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="T3">
+        <v>0.33</v>
+      </c>
+      <c r="U3">
+        <v>5</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
         <v>29</v>
       </c>
-      <c r="S3">
-        <v>1</v>
-      </c>
-      <c r="T3">
-        <v>4.8899999999999997</v>
-      </c>
-      <c r="U3">
-        <v>0.33</v>
-      </c>
-      <c r="V3">
-        <v>5</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
         <v>24</v>
       </c>
-      <c r="C4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
-      </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G4">
         <v>5880</v>
       </c>
       <c r="H4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P4" s="1">
         <v>0.6</v>
       </c>
       <c r="Q4" t="s">
-        <v>29</v>
+        <v>28</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
       </c>
       <c r="S4">
-        <v>1</v>
+        <v>4.8899999999999997</v>
       </c>
       <c r="T4">
-        <v>4.8899999999999997</v>
+        <v>0.33</v>
       </c>
       <c r="U4">
-        <v>0.33</v>
+        <v>5</v>
       </c>
       <c r="V4">
-        <v>5</v>
-      </c>
-      <c r="W4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
         <v>23</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
       </c>
       <c r="C5" t="s">
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G5">
         <v>5880</v>
       </c>
       <c r="H5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" t="s">
         <v>32</v>
       </c>
-      <c r="I5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J5" t="s">
-        <v>33</v>
-      </c>
       <c r="K5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O5">
         <v>15</v>
@@ -1348,66 +1342,66 @@
         <v>0.6</v>
       </c>
       <c r="Q5" t="s">
-        <v>29</v>
-      </c>
-      <c r="S5" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="R5" t="s">
+        <v>25</v>
+      </c>
+      <c r="S5">
+        <v>4.8899999999999997</v>
       </c>
       <c r="T5">
-        <v>4.8899999999999997</v>
+        <v>0.33</v>
       </c>
       <c r="U5">
-        <v>0.33</v>
+        <v>5</v>
       </c>
       <c r="V5">
-        <v>5</v>
-      </c>
-      <c r="W5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
         <v>23</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="s">
         <v>24</v>
       </c>
-      <c r="C6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" t="s">
-        <v>25</v>
-      </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G6">
         <v>5880</v>
       </c>
       <c r="H6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" t="s">
         <v>32</v>
       </c>
-      <c r="I6" t="s">
-        <v>31</v>
-      </c>
-      <c r="J6" t="s">
-        <v>33</v>
-      </c>
       <c r="K6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L6" t="s">
+        <v>34</v>
+      </c>
+      <c r="M6" t="s">
         <v>35</v>
       </c>
-      <c r="M6" t="s">
+      <c r="N6" t="s">
         <v>36</v>
-      </c>
-      <c r="N6" t="s">
-        <v>37</v>
       </c>
       <c r="O6">
         <v>15</v>
@@ -1416,62 +1410,62 @@
         <v>0.6</v>
       </c>
       <c r="Q6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S6" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="R6" t="s">
+        <v>25</v>
+      </c>
+      <c r="S6">
+        <v>4.8899999999999997</v>
       </c>
       <c r="T6">
-        <v>4.8899999999999997</v>
+        <v>0.33</v>
       </c>
       <c r="U6">
-        <v>0.33</v>
+        <v>5</v>
       </c>
       <c r="V6">
-        <v>5</v>
-      </c>
-      <c r="W6">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
@@ -1485,15 +1479,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064FBF1EC94D9E9419E928C7F04731A98" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d5d1fc6aea0bdb544d42f3777360a695">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="307c76f0-d205-4835-9aae-d70c69349486" xmlns:ns3="c1544048-3019-4d62-a7f3-2ad0cae9f9e9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="91955e799b8657f65baef53610b4215d" ns2:_="" ns3:_="">
     <xsd:import namespace="307c76f0-d205-4835-9aae-d70c69349486"/>
@@ -1742,6 +1727,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1754,14 +1748,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B1C7573-D4C2-4CC9-AEAF-DBFC93DE5FD3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{893E3792-6E1A-4ACB-8552-B86A077B5A4D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1780,6 +1766,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B1C7573-D4C2-4CC9-AEAF-DBFC93DE5FD3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{013CA3C2-86F0-4056-AE8C-432415CDD608}">
   <ds:schemaRefs>
